--- a/data/02_clean.xlsx
+++ b/data/02_clean.xlsx
@@ -12648,138 +12648,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.3735</v>
+        <v>48.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6854</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3118</v>
+        <v>27.35</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2502</v>
+        <v>-5.9</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3091</v>
+        <v>130.85</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>inflation_5yr_avg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9053</v>
+        <v>4.002</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0853</v>
+        <v>14.7713</v>
       </c>
       <c r="D3" t="n">
-        <v>0.18</v>
+        <v>10.7692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5453</v>
+        <v>-17.5364</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4453</v>
+        <v>36.3097</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>rq_estimate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.925</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>29.8364</v>
+        <v>-0.4118</v>
       </c>
       <c r="D4" t="n">
-        <v>18.9114</v>
+        <v>0.5776</v>
       </c>
       <c r="E4" t="n">
-        <v>-26.8977</v>
+        <v>-2.1446</v>
       </c>
       <c r="F4" t="n">
-        <v>67.6591</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>co2_pc</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4761</v>
+        <v>0.1868</v>
       </c>
       <c r="C5" t="n">
-        <v>9.988</v>
+        <v>1.155</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5118</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-12.5475</v>
+        <v>-1.7497</v>
       </c>
       <c r="F5" t="n">
-        <v>25.0116</v>
+        <v>3.0914</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pv_estimate</t>
+          <t>primary_gpi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.3848</v>
+        <v>0.9329</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2088</v>
+        <v>1.0124</v>
       </c>
       <c r="D6" t="n">
-        <v>1.176</v>
+        <v>0.0795</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.7369</v>
+        <v>0.774</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1433</v>
+        <v>1.1713</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -12816,23 +12816,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>life_expect_tot</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62.1635</v>
+        <v>34.625</v>
       </c>
       <c r="C8" t="n">
-        <v>68.505</v>
+        <v>42.925</v>
       </c>
       <c r="D8" t="n">
-        <v>6.3415</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>49.4805</v>
+        <v>18.025</v>
       </c>
       <c r="F8" t="n">
-        <v>81.188</v>
+        <v>59.525</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -12844,26 +12844,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>water_access_pop</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.69589999999999</v>
+        <v>74.0596</v>
       </c>
       <c r="C9" t="n">
-        <v>86.95480000000001</v>
+        <v>93.39409999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>22.2589</v>
+        <v>19.3345</v>
       </c>
       <c r="E9" t="n">
-        <v>20.1782</v>
+        <v>35.3905</v>
       </c>
       <c r="F9" t="n">
-        <v>131.4725</v>
+        <v>132.0631</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12872,79 +12872,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gdp_pc_ppp</t>
+          <t>va_estimate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2922.2094</v>
+        <v>-1.2381</v>
       </c>
       <c r="C10" t="n">
-        <v>10340.9953</v>
+        <v>-0.2874</v>
       </c>
       <c r="D10" t="n">
-        <v>7418.7858</v>
+        <v>0.9507</v>
       </c>
       <c r="E10" t="n">
-        <v>-11915.3623</v>
+        <v>-3.1396</v>
       </c>
       <c r="F10" t="n">
-        <v>25178.567</v>
+        <v>1.614</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>freshwater_withdraw</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.1318</v>
+        <v>1.3138</v>
       </c>
       <c r="C11" t="n">
-        <v>41.1461</v>
+        <v>22.4265</v>
       </c>
       <c r="D11" t="n">
-        <v>19.0143</v>
+        <v>21.1128</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.8968</v>
+        <v>-40.9118</v>
       </c>
       <c r="F11" t="n">
-        <v>79.1747</v>
+        <v>64.6521</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>va_estimate</t>
+          <t>water_access_pop</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.2381</v>
+        <v>64.69589999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2874</v>
+        <v>86.95480000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9507</v>
+        <v>22.2589</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1396</v>
+        <v>20.1782</v>
       </c>
       <c r="F12" t="n">
-        <v>1.614</v>
+        <v>131.4725</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -12956,26 +12956,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gdp_growth_3yr_avg</t>
+          <t>pv_estimate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0071</v>
+        <v>-1.3848</v>
       </c>
       <c r="C13" t="n">
-        <v>5.4095</v>
+        <v>-0.2088</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4024</v>
+        <v>1.176</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7976</v>
+        <v>-3.7369</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2142</v>
+        <v>2.1433</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12984,79 +12984,79 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gini</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.625</v>
+        <v>22.1318</v>
       </c>
       <c r="C14" t="n">
-        <v>42.925</v>
+        <v>41.1461</v>
       </c>
       <c r="D14" t="n">
-        <v>8.300000000000001</v>
+        <v>19.0143</v>
       </c>
       <c r="E14" t="n">
-        <v>18.025</v>
+        <v>-15.8968</v>
       </c>
       <c r="F14" t="n">
-        <v>59.525</v>
+        <v>79.1747</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inflation_5yr_avg</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.002</v>
+        <v>71.2967</v>
       </c>
       <c r="C15" t="n">
-        <v>14.7713</v>
+        <v>92.41500000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7692</v>
+        <v>21.1183</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.5364</v>
+        <v>29.06</v>
       </c>
       <c r="F15" t="n">
-        <v>36.3097</v>
+        <v>134.6517</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.8673</v>
+        <v>10.925</v>
       </c>
       <c r="C16" t="n">
-        <v>49.9515</v>
+        <v>29.8364</v>
       </c>
       <c r="D16" t="n">
-        <v>20.0842</v>
+        <v>18.9114</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.3011</v>
+        <v>-26.8977</v>
       </c>
       <c r="F16" t="n">
-        <v>90.1199</v>
+        <v>67.6591</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -13068,51 +13068,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>co2_pc</t>
+          <t>rl_estimate</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1868</v>
+        <v>-1.1916</v>
       </c>
       <c r="C17" t="n">
-        <v>1.155</v>
+        <v>-0.3915</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7497</v>
+        <v>-2.7916</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0914</v>
+        <v>1.2085</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rq_estimate</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.9893999999999999</v>
+        <v>2.4761</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.4118</v>
+        <v>9.988</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5776</v>
+        <v>7.5118</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1446</v>
+        <v>-12.5475</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7433999999999999</v>
+        <v>25.0116</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -13124,82 +13124,82 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>firm_foreign_owned</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48.8</v>
+        <v>7.4251</v>
       </c>
       <c r="C19" t="n">
-        <v>76.15000000000001</v>
+        <v>20.5202</v>
       </c>
       <c r="D19" t="n">
-        <v>27.35</v>
+        <v>13.0951</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.9</v>
+        <v>-18.765</v>
       </c>
       <c r="F19" t="n">
-        <v>130.85</v>
+        <v>46.7104</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rl_estimate</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.1916</v>
+        <v>2.3735</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3915</v>
+        <v>3.6854</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1.3118</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7916</v>
+        <v>-0.2502</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2085</v>
+        <v>6.3091</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cc_estimate</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.1462</v>
+        <v>0.9053</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2973</v>
+        <v>1.0853</v>
       </c>
       <c r="D21" t="n">
-        <v>0.849</v>
+        <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8441</v>
+        <v>0.5453</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4006</v>
+        <v>1.4453</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -13208,51 +13208,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>freshwater_withdraw</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3138</v>
+        <v>0.405</v>
       </c>
       <c r="C22" t="n">
-        <v>22.4265</v>
+        <v>30.5774</v>
       </c>
       <c r="D22" t="n">
-        <v>21.1128</v>
+        <v>30.1723</v>
       </c>
       <c r="E22" t="n">
-        <v>-40.9118</v>
+        <v>-59.9396</v>
       </c>
       <c r="F22" t="n">
-        <v>64.6521</v>
+        <v>90.922</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>agri_land</t>
+          <t>mort_infant</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.5705</v>
+        <v>27.8</v>
       </c>
       <c r="C23" t="n">
-        <v>68.7938</v>
+        <v>46.925</v>
       </c>
       <c r="D23" t="n">
-        <v>36.2233</v>
+        <v>19.125</v>
       </c>
       <c r="E23" t="n">
-        <v>-39.8762</v>
+        <v>-10.45</v>
       </c>
       <c r="F23" t="n">
-        <v>141.2405</v>
+        <v>85.175</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -13264,51 +13264,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>gdp_pc_ppp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>71.2967</v>
+        <v>2922.2094</v>
       </c>
       <c r="C24" t="n">
-        <v>92.41500000000001</v>
+        <v>10340.9953</v>
       </c>
       <c r="D24" t="n">
-        <v>21.1183</v>
+        <v>7418.7858</v>
       </c>
       <c r="E24" t="n">
-        <v>29.06</v>
+        <v>-11915.3623</v>
       </c>
       <c r="F24" t="n">
-        <v>134.6517</v>
+        <v>25178.567</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nonrenew_elec</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.4792</v>
+        <v>29.8673</v>
       </c>
       <c r="C25" t="n">
-        <v>91.8817</v>
+        <v>49.9515</v>
       </c>
       <c r="D25" t="n">
-        <v>64.40260000000001</v>
+        <v>20.0842</v>
       </c>
       <c r="E25" t="n">
-        <v>-101.3259</v>
+        <v>-10.3011</v>
       </c>
       <c r="F25" t="n">
-        <v>220.6868</v>
+        <v>90.1199</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -13320,26 +13320,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>life_expect_tot</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>72.7272</v>
+        <v>62.1635</v>
       </c>
       <c r="C26" t="n">
-        <v>89.1845</v>
+        <v>68.505</v>
       </c>
       <c r="D26" t="n">
-        <v>16.4572</v>
+        <v>6.3415</v>
       </c>
       <c r="E26" t="n">
-        <v>39.8128</v>
+        <v>49.4805</v>
       </c>
       <c r="F26" t="n">
-        <v>122.0989</v>
+        <v>81.188</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -13348,23 +13348,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74.0596</v>
+        <v>72.7272</v>
       </c>
       <c r="C27" t="n">
-        <v>93.39409999999999</v>
+        <v>89.1845</v>
       </c>
       <c r="D27" t="n">
-        <v>19.3345</v>
+        <v>16.4572</v>
       </c>
       <c r="E27" t="n">
-        <v>35.3905</v>
+        <v>39.8128</v>
       </c>
       <c r="F27" t="n">
-        <v>132.0631</v>
+        <v>122.0989</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -13376,26 +13376,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mort_infant</t>
+          <t>gdp_growth_3yr_avg</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.8</v>
+        <v>3.0071</v>
       </c>
       <c r="C28" t="n">
-        <v>46.925</v>
+        <v>5.4095</v>
       </c>
       <c r="D28" t="n">
-        <v>19.125</v>
+        <v>2.4024</v>
       </c>
       <c r="E28" t="n">
-        <v>-10.45</v>
+        <v>-1.7976</v>
       </c>
       <c r="F28" t="n">
-        <v>85.175</v>
+        <v>10.2142</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -13404,51 +13404,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>cc_estimate</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.405</v>
+        <v>-1.1462</v>
       </c>
       <c r="C29" t="n">
-        <v>30.5774</v>
+        <v>-0.2973</v>
       </c>
       <c r="D29" t="n">
-        <v>30.1723</v>
+        <v>0.849</v>
       </c>
       <c r="E29" t="n">
-        <v>-59.9396</v>
+        <v>-2.8441</v>
       </c>
       <c r="F29" t="n">
-        <v>90.922</v>
+        <v>1.4006</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ge_estimate</t>
+          <t>nonrenew_elec</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.1413</v>
+        <v>27.4792</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3145</v>
+        <v>91.8817</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8269</v>
+        <v>64.40260000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.7951</v>
+        <v>-101.3259</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3393</v>
+        <v>220.6868</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -13460,51 +13460,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7.4251</v>
+        <v>10.3687</v>
       </c>
       <c r="C31" t="n">
-        <v>20.5202</v>
+        <v>36.9497</v>
       </c>
       <c r="D31" t="n">
-        <v>13.0951</v>
+        <v>26.581</v>
       </c>
       <c r="E31" t="n">
-        <v>-18.765</v>
+        <v>-42.7934</v>
       </c>
       <c r="F31" t="n">
-        <v>46.7104</v>
+        <v>90.1117</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>social_protection_labour_pop</t>
+          <t>agri_land</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10.3687</v>
+        <v>32.5705</v>
       </c>
       <c r="C32" t="n">
-        <v>36.9497</v>
+        <v>68.7938</v>
       </c>
       <c r="D32" t="n">
-        <v>26.581</v>
+        <v>36.2233</v>
       </c>
       <c r="E32" t="n">
-        <v>-42.7934</v>
+        <v>-39.8762</v>
       </c>
       <c r="F32" t="n">
-        <v>90.1117</v>
+        <v>141.2405</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -13516,26 +13516,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>primary_gpi</t>
+          <t>ge_estimate</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9329</v>
+        <v>-1.1413</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0124</v>
+        <v>-0.3145</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0795</v>
+        <v>0.8269</v>
       </c>
       <c r="E33" t="n">
-        <v>0.774</v>
+        <v>-2.7951</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1713</v>
+        <v>1.3393</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>

--- a/data/02_clean.xlsx
+++ b/data/02_clean.xlsx
@@ -792,12 +792,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Firms with at least 10% foreign ownership (% of firms)</t>
+          <t>Domestic credit to private sector (% of GDP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1803,7 +1803,7 @@
         <v>0.862</v>
       </c>
       <c r="D2" t="n">
-        <v>0.607</v>
+        <v>0.634</v>
       </c>
       <c r="E2" t="n">
         <v>0.552</v>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.426</v>
+        <v>0.448</v>
       </c>
       <c r="E3" t="n">
         <v>0.431</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.607</v>
+        <v>0.634</v>
       </c>
       <c r="C4" t="n">
-        <v>0.426</v>
+        <v>0.448</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1853,7 +1853,7 @@
         <v>0.765</v>
       </c>
       <c r="F4" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
@@ -1891,7 +1891,7 @@
         <v>0.358</v>
       </c>
       <c r="D6" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="E6" t="n">
         <v>0.43</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>-0.6397452</v>
       </c>
       <c r="H2" t="n">
-        <v>17620.7423956126</v>
+        <v>17646.332598878</v>
       </c>
       <c r="I2" t="n">
         <v>3.800000000029527</v>
@@ -2123,7 +2123,7 @@
         <v>27.6</v>
       </c>
       <c r="L2" t="n">
-        <v>7.43725678375</v>
+        <v>19.0341413218985</v>
       </c>
       <c r="M2" t="n">
         <v>93.76999664306641</v>
@@ -2217,7 +2217,7 @@
         <v>-0.816904499999999</v>
       </c>
       <c r="H3" t="n">
-        <v>19094.1449444111</v>
+        <v>19121.874936645</v>
       </c>
       <c r="I3" t="n">
         <v>4.249098466440747</v>
@@ -2229,7 +2229,7 @@
         <v>28.5</v>
       </c>
       <c r="L3" t="n">
-        <v>4.554225445</v>
+        <v>27.5692279729149</v>
       </c>
       <c r="M3" t="n">
         <v>95.19086762261399</v>
@@ -2323,7 +2323,7 @@
         <v>-1.5426693</v>
       </c>
       <c r="H4" t="n">
-        <v>14303.8087736988</v>
+        <v>14324.5818697336</v>
       </c>
       <c r="I4" t="n">
         <v>1.26672739783939</v>
@@ -2335,7 +2335,7 @@
         <v>32.7</v>
       </c>
       <c r="L4" t="n">
-        <v>7.43725678375</v>
+        <v>13.041851907924</v>
       </c>
       <c r="M4" t="n">
         <v>88.41017364659312</v>
@@ -2395,7 +2395,7 @@
         <v>8.723871011741711</v>
       </c>
       <c r="AF4" t="n">
-        <v>73.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>96.35454408616189</v>
@@ -2429,7 +2429,7 @@
         <v>-0.5521901</v>
       </c>
       <c r="H5" t="n">
-        <v>10415.1240234375</v>
+        <v>10430.2490234375</v>
       </c>
       <c r="I5" t="n">
         <v>3.087233897305676</v>
@@ -2441,7 +2441,7 @@
         <v>39.5</v>
       </c>
       <c r="L5" t="n">
-        <v>12.68201256</v>
+        <v>54.7085229571242</v>
       </c>
       <c r="M5" t="n">
         <v>89.120002746582</v>
@@ -2535,7 +2535,7 @@
         <v>-1.4513517</v>
       </c>
       <c r="H6" t="n">
-        <v>2115.81616210938</v>
+        <v>2118.88891601563</v>
       </c>
       <c r="I6" t="n">
         <v>-1.797641754412704</v>
@@ -2547,7 +2547,7 @@
         <v>34.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.22802484</v>
+        <v>5.63980468495649</v>
       </c>
       <c r="M6" t="n">
         <v>65.80999755859381</v>
@@ -2641,7 +2641,7 @@
         <v>-0.192361099999999</v>
       </c>
       <c r="H7" t="n">
-        <v>14521.0080937638</v>
+        <v>14542.0966234293</v>
       </c>
       <c r="I7" t="n">
         <v>1.516916269427805</v>
@@ -2653,7 +2653,7 @@
         <v>33.7</v>
       </c>
       <c r="L7" t="n">
-        <v>11.28476429</v>
+        <v>54.7085229571242</v>
       </c>
       <c r="M7" t="n">
         <v>98.1600036621094</v>
@@ -2747,7 +2747,7 @@
         <v>-0.1047671</v>
       </c>
       <c r="H8" t="n">
-        <v>4434.5642184028</v>
+        <v>4441.00443511982</v>
       </c>
       <c r="I8" t="n">
         <v>6.686280033814153</v>
@@ -2759,7 +2759,7 @@
         <v>34.4</v>
       </c>
       <c r="L8" t="n">
-        <v>21.05908012</v>
+        <v>18.9801611697157</v>
       </c>
       <c r="M8" t="n">
         <v>71.25</v>
@@ -2819,7 +2819,7 @@
         <v>41.8300133025896</v>
       </c>
       <c r="AF8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AG8" t="n">
         <v>69.5868397867067</v>
@@ -2853,7 +2853,7 @@
         <v>-0.2479719</v>
       </c>
       <c r="H9" t="n">
-        <v>2895.89152033665</v>
+        <v>2901.04214238045</v>
       </c>
       <c r="I9" t="n">
         <v>3.153654947299756</v>
@@ -2865,7 +2865,7 @@
         <v>37.4</v>
       </c>
       <c r="L9" t="n">
-        <v>8.357632637</v>
+        <v>27.143359333582</v>
       </c>
       <c r="M9" t="n">
         <v>62.810001373291</v>
@@ -2925,7 +2925,7 @@
         <v>53.4020054824561</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.7</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
         <v>49.9986600107497</v>
@@ -2959,7 +2959,7 @@
         <v>0.8619303</v>
       </c>
       <c r="H10" t="n">
-        <v>11195.1205312923</v>
+        <v>11184.7207350908</v>
       </c>
       <c r="I10" t="n">
         <v>9.20910662855335</v>
@@ -2971,7 +2971,7 @@
         <v>42.4</v>
       </c>
       <c r="L10" t="n">
-        <v>25.16181755</v>
+        <v>54.6131421681783</v>
       </c>
       <c r="M10" t="n">
         <v>98.3199996948242</v>
@@ -3031,7 +3031,7 @@
         <v>19.6029776674938</v>
       </c>
       <c r="AF10" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG10" t="n">
         <v>92.2800892661912</v>
@@ -3065,7 +3065,7 @@
         <v>-0.296167199999999</v>
       </c>
       <c r="H11" t="n">
-        <v>3475.61245701341</v>
+        <v>3480.66001035486</v>
       </c>
       <c r="I11" t="n">
         <v>5.653684884554643</v>
@@ -3077,7 +3077,7 @@
         <v>38.8</v>
       </c>
       <c r="L11" t="n">
-        <v>17.59476089</v>
+        <v>9.40397496213459</v>
       </c>
       <c r="M11" t="n">
         <v>67.4899978637695</v>
@@ -3137,7 +3137,7 @@
         <v>62.6482213438735</v>
       </c>
       <c r="AF11" t="n">
-        <v>66.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="AG11" t="n">
         <v>87.1034800376148</v>
@@ -3171,7 +3171,7 @@
         <v>-0.1303327</v>
       </c>
       <c r="H12" t="n">
-        <v>8019.99702389611</v>
+        <v>8051.19381149848</v>
       </c>
       <c r="I12" t="n">
         <v>4.264136441795366</v>
@@ -3183,7 +3183,7 @@
         <v>43.5</v>
       </c>
       <c r="L12" t="n">
-        <v>11.18939304</v>
+        <v>8.92435396216065</v>
       </c>
       <c r="M12" t="n">
         <v>91.5100021362305</v>
@@ -3243,7 +3243,7 @@
         <v>55.393019913595</v>
       </c>
       <c r="AF12" t="n">
-        <v>89.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>89.9220116872755</v>
@@ -3277,7 +3277,7 @@
         <v>-1.0078531</v>
       </c>
       <c r="H13" t="n">
-        <v>4565.3007888456</v>
+        <v>4571.93087130821</v>
       </c>
       <c r="I13" t="n">
         <v>4.954727039592293</v>
@@ -3289,7 +3289,7 @@
         <v>29.6</v>
       </c>
       <c r="L13" t="n">
-        <v>7.270904541</v>
+        <v>10.6668743226753</v>
       </c>
       <c r="M13" t="n">
         <v>53.939998626709</v>
@@ -3349,7 +3349,7 @@
         <v>73.2292487384014</v>
       </c>
       <c r="AF13" t="n">
-        <v>51.1</v>
+        <v>53.8</v>
       </c>
       <c r="AG13" t="n">
         <v>74.1924841600776</v>
@@ -3383,7 +3383,7 @@
         <v>-1.1549527</v>
       </c>
       <c r="H14" t="n">
-        <v>3119.37157047437</v>
+        <v>3093.46533465682</v>
       </c>
       <c r="I14" t="n">
         <v>4.83249520601558</v>
@@ -3395,7 +3395,7 @@
         <v>33.4</v>
       </c>
       <c r="L14" t="n">
-        <v>9.242378235</v>
+        <v>10.7253688584545</v>
       </c>
       <c r="M14" t="n">
         <v>82.23000335693359</v>
@@ -3455,7 +3455,7 @@
         <v>29.8908428165007</v>
       </c>
       <c r="AF14" t="n">
-        <v>40.5</v>
+        <v>43.7</v>
       </c>
       <c r="AG14" t="n">
         <v>61.8077030171668</v>
@@ -3489,7 +3489,7 @@
         <v>-0.3616761</v>
       </c>
       <c r="H15" t="n">
-        <v>7669.23195715687</v>
+        <v>7680.36980823038</v>
       </c>
       <c r="I15" t="n">
         <v>6.339806232931057</v>
@@ -3501,7 +3501,7 @@
         <v>35.3</v>
       </c>
       <c r="L15" t="n">
-        <v>22.52928162</v>
+        <v>22.5184329531641</v>
       </c>
       <c r="M15" t="n">
         <v>66.8399963378906</v>
@@ -3561,7 +3561,7 @@
         <v>86.47581635220131</v>
       </c>
       <c r="AF15" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AG15" t="n">
         <v>77.2470593822361</v>
@@ -3595,7 +3595,7 @@
         <v>-1.01213</v>
       </c>
       <c r="H16" t="n">
-        <v>1871.04406164262</v>
+        <v>1873.76133636244</v>
       </c>
       <c r="I16" t="n">
         <v>4.504572236722669</v>
@@ -3607,7 +3607,7 @@
         <v>35.3</v>
       </c>
       <c r="L16" t="n">
-        <v>23.03652573</v>
+        <v>14.787430409394</v>
       </c>
       <c r="M16" t="n">
         <v>75.06</v>
@@ -3667,7 +3667,7 @@
         <v>19.9651162790698</v>
       </c>
       <c r="AF16" t="n">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="AG16" t="n">
         <v>78.8278345445612</v>
@@ -3701,7 +3701,7 @@
         <v>-0.8493558999999991</v>
       </c>
       <c r="H17" t="n">
-        <v>3314.77332231959</v>
+        <v>3321.57614442921</v>
       </c>
       <c r="I17" t="n">
         <v>4.494555689440343</v>
@@ -3713,7 +3713,7 @@
         <v>35.7</v>
       </c>
       <c r="L17" t="n">
-        <v>3.442505121</v>
+        <v>22.3956105371061</v>
       </c>
       <c r="M17" t="n">
         <v>50.3300018310547</v>
@@ -3773,7 +3773,7 @@
         <v>35.4694668863046</v>
       </c>
       <c r="AF17" t="n">
-        <v>54.5</v>
+        <v>49.5</v>
       </c>
       <c r="AG17" t="n">
         <v>86.3633567815443</v>
@@ -3807,7 +3807,7 @@
         <v>-0.7965253</v>
       </c>
       <c r="H18" t="n">
-        <v>7368.75275290214</v>
+        <v>7379.45422386145</v>
       </c>
       <c r="I18" t="n">
         <v>6.637699047698677</v>
@@ -3819,7 +3819,7 @@
         <v>32</v>
       </c>
       <c r="L18" t="n">
-        <v>12.41186714</v>
+        <v>22.7235411550392</v>
       </c>
       <c r="M18" t="n">
         <v>70.86000061035161</v>
@@ -3879,7 +3879,7 @@
         <v>38.5272145144077</v>
       </c>
       <c r="AF18" t="n">
-        <v>50.3</v>
+        <v>52.2</v>
       </c>
       <c r="AG18" t="n">
         <v>77.28464913753881</v>
@@ -3913,7 +3913,7 @@
         <v>-0.517433</v>
       </c>
       <c r="H19" t="n">
-        <v>2049.93305251019</v>
+        <v>2044.04904937758</v>
       </c>
       <c r="I19" t="n">
         <v>7.72666337784132</v>
@@ -3925,7 +3925,7 @@
         <v>32.9</v>
       </c>
       <c r="L19" t="n">
-        <v>9.647658348</v>
+        <v>10.2781507372819</v>
       </c>
       <c r="M19" t="n">
         <v>53.9099998474121</v>
@@ -3985,7 +3985,7 @@
         <v>36.7873213862793</v>
       </c>
       <c r="AF19" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
       <c r="AG19" t="n">
         <v>53.4274656286176</v>
@@ -4019,7 +4019,7 @@
         <v>-1.098731</v>
       </c>
       <c r="H20" t="n">
-        <v>9086.87550609627</v>
+        <v>9099.869438636761</v>
       </c>
       <c r="I20" t="n">
         <v>3.901933224720923</v>
@@ -4031,7 +4031,7 @@
         <v>33.9</v>
       </c>
       <c r="L20" t="n">
-        <v>9.247492790000001</v>
+        <v>9.5616917667191</v>
       </c>
       <c r="M20" t="n">
         <v>81.36000061035161</v>
@@ -4091,7 +4091,7 @@
         <v>76.1972932793131</v>
       </c>
       <c r="AF20" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
       <c r="AG20" t="n">
         <v>82.2488935172216</v>
@@ -4125,7 +4125,7 @@
         <v>0.0381077</v>
       </c>
       <c r="H21" t="n">
-        <v>5070.6486207418</v>
+        <v>5097.24318834766</v>
       </c>
       <c r="I21" t="n">
         <v>4.856689514885733</v>
@@ -4137,7 +4137,7 @@
         <v>36.2</v>
       </c>
       <c r="L21" t="n">
-        <v>11.36375141</v>
+        <v>29.8119196212555</v>
       </c>
       <c r="M21" t="n">
         <v>67.4499969482422</v>
@@ -4197,7 +4197,7 @@
         <v>49.4000934919233</v>
       </c>
       <c r="AF21" t="n">
-        <v>74.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AG21" t="n">
         <v>88.0435670438381</v>
@@ -4231,7 +4231,7 @@
         <v>-0.568678999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>3522.30588009119</v>
+        <v>3527.42124292431</v>
       </c>
       <c r="I22" t="n">
         <v>5.105599952139404</v>
@@ -4243,7 +4243,7 @@
         <v>35.7</v>
       </c>
       <c r="L22" t="n">
-        <v>3.163730145</v>
+        <v>3.96782641222454</v>
       </c>
       <c r="M22" t="n">
         <v>72.9899978637695</v>
@@ -4303,7 +4303,7 @@
         <v>54.7104461069548</v>
       </c>
       <c r="AF22" t="n">
-        <v>35.5</v>
+        <v>39.2</v>
       </c>
       <c r="AG22" t="n">
         <v>68.0790238061869</v>
@@ -4337,7 +4337,7 @@
         <v>-0.5879504</v>
       </c>
       <c r="H23" t="n">
-        <v>3365.45809007306</v>
+        <v>3814.83532681353</v>
       </c>
       <c r="I23" t="n">
         <v>6.339526793984713</v>
@@ -4349,7 +4349,7 @@
         <v>37.9</v>
       </c>
       <c r="L23" t="n">
-        <v>17.04686165</v>
+        <v>25.3652125489184</v>
       </c>
       <c r="M23" t="n">
         <v>90.36000061035161</v>
@@ -4409,7 +4409,7 @@
         <v>70.23349880492739</v>
       </c>
       <c r="AF23" t="n">
-        <v>59.2</v>
+        <v>61.1</v>
       </c>
       <c r="AG23" t="n">
         <v>64.7862455498292</v>
@@ -4443,7 +4443,7 @@
         <v>-0.6242518</v>
       </c>
       <c r="H24" t="n">
-        <v>10118.6089945408</v>
+        <v>9963.590208742869</v>
       </c>
       <c r="I24" t="n">
         <v>3.276778847275513</v>
@@ -4455,7 +4455,7 @@
         <v>51.3</v>
       </c>
       <c r="L24" t="n">
-        <v>17.50716972</v>
+        <v>7.16892640926562</v>
       </c>
       <c r="M24" t="n">
         <v>80.6999969482422</v>
@@ -4513,7 +4513,7 @@
         <v>36.9479425683805</v>
       </c>
       <c r="AF24" t="n">
-        <v>51.1</v>
+        <v>55.5</v>
       </c>
       <c r="AG24" t="n">
         <v>67.9607422242112</v>
@@ -4547,7 +4547,7 @@
         <v>-1.1264261</v>
       </c>
       <c r="H25" t="n">
-        <v>5588.98645861945</v>
+        <v>5597.10321648993</v>
       </c>
       <c r="I25" t="n">
         <v>3.53635666455528</v>
@@ -4559,7 +4559,7 @@
         <v>42.2</v>
       </c>
       <c r="L25" t="n">
-        <v>9.873967171</v>
+        <v>14.0910928751244</v>
       </c>
       <c r="M25" t="n">
         <v>81.88999938964839</v>
@@ -4653,7 +4653,7 @@
         <v>-1.3816342</v>
       </c>
       <c r="H26" t="n">
-        <v>1263.10234213699</v>
+        <v>1264.93671692975</v>
       </c>
       <c r="I26" t="n">
         <v>0.8846234252278924</v>
@@ -4665,7 +4665,7 @@
         <v>43</v>
       </c>
       <c r="L26" t="n">
-        <v>27.81489944</v>
+        <v>13.0385826544527</v>
       </c>
       <c r="M26" t="n">
         <v>50.5999984741211</v>
@@ -4725,7 +4725,7 @@
         <v>9.09948955022633</v>
       </c>
       <c r="AF26" t="n">
-        <v>17.6</v>
+        <v>18.2</v>
       </c>
       <c r="AG26" t="n">
         <v>36.5040268237207</v>
@@ -4759,7 +4759,7 @@
         <v>-1.48878199999999</v>
       </c>
       <c r="H27" t="n">
-        <v>2742.65952183613</v>
+        <v>2766.98134913811</v>
       </c>
       <c r="I27" t="n">
         <v>4.360138972456734</v>
@@ -4771,7 +4771,7 @@
         <v>37.4</v>
       </c>
       <c r="L27" t="n">
-        <v>7.421092987</v>
+        <v>8.322909548913341</v>
       </c>
       <c r="M27" t="n">
         <v>45.1300010681152</v>
@@ -4829,7 +4829,7 @@
         <v>39.9756194409149</v>
       </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>13.4</v>
       </c>
       <c r="AG27" t="n">
         <v>52.2090525523694</v>
@@ -4863,7 +4863,7 @@
         <v>-1.4043963</v>
       </c>
       <c r="H28" t="n">
-        <v>7026.36223281494</v>
+        <v>7003.66225819816</v>
       </c>
       <c r="I28" t="n">
         <v>1.82740319198802</v>
@@ -4875,7 +4875,7 @@
         <v>48.9</v>
       </c>
       <c r="L28" t="n">
-        <v>22.62924385</v>
+        <v>13.7900478506587</v>
       </c>
       <c r="M28" t="n">
         <v>78.5699996948242</v>
@@ -4933,7 +4933,7 @@
         <v>31.1900439238653</v>
       </c>
       <c r="AF28" t="n">
-        <v>51.3</v>
+        <v>53</v>
       </c>
       <c r="AG28" t="n">
         <v>73.4884211673414</v>
@@ -4967,7 +4967,7 @@
         <v>-1.4890974</v>
       </c>
       <c r="H29" t="n">
-        <v>1821.04868718058</v>
+        <v>1823.27705135453</v>
       </c>
       <c r="I29" t="n">
         <v>7.982396238926861</v>
@@ -4979,7 +4979,7 @@
         <v>44.7</v>
       </c>
       <c r="L29" t="n">
-        <v>4.44111824</v>
+        <v>11.2863136949009</v>
       </c>
       <c r="M29" t="n">
         <v>77.90000152587891</v>
@@ -5037,7 +5037,7 @@
         <v>15.480763018019</v>
       </c>
       <c r="AF29" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="AG29" t="n">
         <v>35.6813611952254</v>
@@ -5071,7 +5071,7 @@
         <v>-1.52463899999999</v>
       </c>
       <c r="H30" t="n">
-        <v>17566.7600284073</v>
+        <v>17072.4273818835</v>
       </c>
       <c r="I30" t="n">
         <v>-1.26844049322483</v>
@@ -5083,7 +5083,7 @@
         <v>38.5</v>
       </c>
       <c r="L30" t="n">
-        <v>46.71037151762501</v>
+        <v>5.81219669046931</v>
       </c>
       <c r="M30" t="n">
         <v>72.68142863682337</v>
@@ -5141,7 +5141,7 @@
         <v>3.73333333333333</v>
       </c>
       <c r="AF30" t="n">
-        <v>66.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AG30" t="n">
         <v>64.6658128879178</v>
@@ -5175,7 +5175,7 @@
         <v>-0.9748427</v>
       </c>
       <c r="H31" t="n">
-        <v>21510.1725307344</v>
+        <v>21541.4112646776</v>
       </c>
       <c r="I31" t="n">
         <v>2.95686338029518</v>
@@ -5187,7 +5187,7 @@
         <v>38</v>
       </c>
       <c r="L31" t="n">
-        <v>46.71037151762501</v>
+        <v>13.3764779657931</v>
       </c>
       <c r="M31" t="n">
         <v>93.98000335693359</v>
@@ -5245,7 +5245,7 @@
         <v>8.35656459812939</v>
       </c>
       <c r="AF31" t="n">
-        <v>94.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AG31" t="n">
         <v>88.5995009085574</v>
@@ -5279,7 +5279,7 @@
         <v>-1.29205449999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1194.94681370387</v>
+        <v>1193.03528498996</v>
       </c>
       <c r="I32" t="n">
         <v>3.228247986906433</v>
@@ -5291,7 +5291,7 @@
         <v>37.5</v>
       </c>
       <c r="L32" t="n">
-        <v>20.62626076</v>
+        <v>38.2575729210921</v>
       </c>
       <c r="M32" t="n">
         <v>88.3979336343743</v>
@@ -5351,7 +5351,7 @@
         <v>83.88655763239871</v>
       </c>
       <c r="AF32" t="n">
-        <v>11.6</v>
+        <v>20.1</v>
       </c>
       <c r="AG32" t="n">
         <v>65.9191041847553</v>
@@ -5385,7 +5385,7 @@
         <v>-0.905052699999999</v>
       </c>
       <c r="H33" t="n">
-        <v>7810.27869066792</v>
+        <v>7821.62138070711</v>
       </c>
       <c r="I33" t="n">
         <v>6.31811899844672</v>
@@ -5397,7 +5397,7 @@
         <v>41.6</v>
       </c>
       <c r="L33" t="n">
-        <v>12.83908081</v>
+        <v>23.1025276600186</v>
       </c>
       <c r="M33" t="n">
         <v>79.5520825495239</v>
@@ -5457,7 +5457,7 @@
         <v>73.5073339085419</v>
       </c>
       <c r="AF33" t="n">
-        <v>65.2</v>
+        <v>69.2</v>
       </c>
       <c r="AG33" t="n">
         <v>79.661532568521</v>
@@ -5503,7 +5503,7 @@
         <v>42.1</v>
       </c>
       <c r="L34" t="n">
-        <v>2.077909231</v>
+        <v>53.241077381173</v>
       </c>
       <c r="M34" t="n">
         <v>86.9700012207031</v>
@@ -5563,7 +5563,7 @@
         <v>62.6515330315189</v>
       </c>
       <c r="AF34" t="n">
-        <v>54.4</v>
+        <v>55.3</v>
       </c>
       <c r="AG34" t="n">
         <v>51.8497177620962</v>
@@ -5597,7 +5597,7 @@
         <v>-0.4629488</v>
       </c>
       <c r="H35" t="n">
-        <v>3287.53492158893</v>
+        <v>3292.3093336937</v>
       </c>
       <c r="I35" t="n">
         <v>6.509593450522286</v>
@@ -5609,7 +5609,7 @@
         <v>31.1</v>
       </c>
       <c r="L35" t="n">
-        <v>6.531822681</v>
+        <v>17.7101483486321</v>
       </c>
       <c r="M35" t="n">
         <v>84.69000244140619</v>
@@ -5669,7 +5669,7 @@
         <v>34.0779564851996</v>
       </c>
       <c r="AF35" t="n">
-        <v>55.4</v>
+        <v>56.6</v>
       </c>
       <c r="AG35" t="n">
         <v>55.5960696159493</v>
@@ -5703,7 +5703,7 @@
         <v>-0.7594497</v>
       </c>
       <c r="H36" t="n">
-        <v>6644.13093243895</v>
+        <v>6649.67919174449</v>
       </c>
       <c r="I36" t="n">
         <v>5.080056466913661</v>
@@ -5715,7 +5715,7 @@
         <v>38.5</v>
       </c>
       <c r="L36" t="n">
-        <v>9.797154427000001</v>
+        <v>31.7980848696513</v>
       </c>
       <c r="M36" t="n">
         <v>93.18000000000001</v>
@@ -5775,7 +5775,7 @@
         <v>49.5263223856783</v>
       </c>
       <c r="AF36" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
       <c r="AG36" t="n">
         <v>65.5965968528709</v>
@@ -5809,7 +5809,7 @@
         <v>-0.627533999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>1857.61756950305</v>
+        <v>1860.31534523381</v>
       </c>
       <c r="I37" t="n">
         <v>1.513433990352425</v>
@@ -5821,7 +5821,7 @@
         <v>38.5</v>
       </c>
       <c r="L37" t="n">
-        <v>20.63000107</v>
+        <v>7.91033846538175</v>
       </c>
       <c r="M37" t="n">
         <v>80.73000335693359</v>
@@ -5915,7 +5915,7 @@
         <v>-0.904286399999999</v>
       </c>
       <c r="H38" t="n">
-        <v>1705.37919520416</v>
+        <v>1708.3035966667</v>
       </c>
       <c r="I38" t="n">
         <v>4.00735919241212</v>
@@ -5927,7 +5927,7 @@
         <v>49.6</v>
       </c>
       <c r="L38" t="n">
-        <v>23.00078201</v>
+        <v>17.6069907113773</v>
       </c>
       <c r="M38" t="n">
         <v>71.43662914417671</v>
@@ -5987,7 +5987,7 @@
         <v>52.7891502835779</v>
       </c>
       <c r="AF38" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="AG38" t="n">
         <v>66.62524413426711</v>
@@ -6021,7 +6021,7 @@
         <v>0.6808504</v>
       </c>
       <c r="H39" t="n">
-        <v>3710.86040434596</v>
+        <v>3784.9629495071</v>
       </c>
       <c r="I39" t="n">
         <v>8.53726263636795</v>
@@ -6033,7 +6033,7 @@
         <v>39.4</v>
       </c>
       <c r="L39" t="n">
-        <v>7.386345387</v>
+        <v>21.3238078981665</v>
       </c>
       <c r="M39" t="n">
         <v>89.9700012207031</v>
@@ -6093,7 +6093,7 @@
         <v>76.3328334008918</v>
       </c>
       <c r="AF39" t="n">
-        <v>63.9</v>
+        <v>72</v>
       </c>
       <c r="AG39" t="n">
         <v>61.392176021167</v>
@@ -6127,7 +6127,7 @@
         <v>-1.61685259999999</v>
       </c>
       <c r="H40" t="n">
-        <v>1601.96466602339</v>
+        <v>1604.29116285918</v>
       </c>
       <c r="I40" t="n">
         <v>3.668282651348444</v>
@@ -6139,7 +6139,7 @@
         <v>42.1</v>
       </c>
       <c r="L40" t="n">
-        <v>15.39827190992308</v>
+        <v>5.43098050942767</v>
       </c>
       <c r="M40" t="n">
         <v>70.7099990844727</v>
@@ -6199,7 +6199,7 @@
         <v>70.34335448082381</v>
       </c>
       <c r="AF40" t="n">
-        <v>50.3</v>
+        <v>54.4</v>
       </c>
       <c r="AG40" t="n">
         <v>75.29479645713771</v>
@@ -6245,7 +6245,7 @@
         <v>44</v>
       </c>
       <c r="L41" t="n">
-        <v>43.72815323</v>
+        <v>5.76315463209053</v>
       </c>
       <c r="M41" t="n">
         <v>36.7000007629395</v>
@@ -6339,7 +6339,7 @@
         <v>-0.346236</v>
       </c>
       <c r="H42" t="n">
-        <v>4220.79638671875</v>
+        <v>4226.92626953125</v>
       </c>
       <c r="I42" t="n">
         <v>5.05394770897933</v>
@@ -6351,7 +6351,7 @@
         <v>40.5</v>
       </c>
       <c r="L42" t="n">
-        <v>6.582366943</v>
+        <v>16.6720456471052</v>
       </c>
       <c r="M42" t="n">
         <v>87.0699996948242</v>
@@ -6411,7 +6411,7 @@
         <v>44.6163919620682</v>
       </c>
       <c r="AF42" t="n">
-        <v>48.3</v>
+        <v>52.4</v>
       </c>
       <c r="AG42" t="n">
         <v>64.6059619473789</v>
@@ -6445,7 +6445,7 @@
         <v>-0.996690299999999</v>
       </c>
       <c r="H43" t="n">
-        <v>3273.2671741364</v>
+        <v>3278.02086557843</v>
       </c>
       <c r="I43" t="n">
         <v>5.326858545229437</v>
@@ -6457,7 +6457,7 @@
         <v>42.7</v>
       </c>
       <c r="L43" t="n">
-        <v>10.42019749</v>
+        <v>14.3001761811715</v>
       </c>
       <c r="M43" t="n">
         <v>85.15000152587891</v>
@@ -6517,7 +6517,7 @@
         <v>71.8880909634949</v>
       </c>
       <c r="AF43" t="n">
-        <v>51.5</v>
+        <v>55.3</v>
       </c>
       <c r="AG43" t="n">
         <v>63.0058015721971</v>
@@ -6551,7 +6551,7 @@
         <v>-0.39812</v>
       </c>
       <c r="H44" t="n">
-        <v>4214.89277804799</v>
+        <v>4221.01397093025</v>
       </c>
       <c r="I44" t="n">
         <v>4.799738237892989</v>
@@ -6563,7 +6563,7 @@
         <v>51.5</v>
       </c>
       <c r="L44" t="n">
-        <v>25.67836571</v>
+        <v>17.0073799722572</v>
       </c>
       <c r="M44" t="n">
         <v>77.65000152587891</v>
@@ -6623,7 +6623,7 @@
         <v>32.0679589448338</v>
       </c>
       <c r="AF44" t="n">
-        <v>51.1</v>
+        <v>53.6</v>
       </c>
       <c r="AG44" t="n">
         <v>73.4120376414689</v>
@@ -6657,7 +6657,7 @@
         <v>-1.1914608</v>
       </c>
       <c r="H45" t="n">
-        <v>5928.0806252756</v>
+        <v>5932.87021993648</v>
       </c>
       <c r="I45" t="n">
         <v>4.388875538633516</v>
@@ -6669,7 +6669,7 @@
         <v>50.3</v>
       </c>
       <c r="L45" t="n">
-        <v>10.87909508</v>
+        <v>6.47769726494533</v>
       </c>
       <c r="M45" t="n">
         <v>92.5100021362305</v>
@@ -6763,7 +6763,7 @@
         <v>0.6066871</v>
       </c>
       <c r="H46" t="n">
-        <v>20538.1320178889</v>
+        <v>20612.4785435561</v>
       </c>
       <c r="I46" t="n">
         <v>1.971398456683194</v>
@@ -6775,7 +6775,7 @@
         <v>54.9</v>
       </c>
       <c r="L46" t="n">
-        <v>17.36618233</v>
+        <v>33.1256504356331</v>
       </c>
       <c r="M46" t="n">
         <v>96.11000061035158</v>
@@ -6833,7 +6833,7 @@
         <v>45.63372328975</v>
       </c>
       <c r="AF46" t="n">
-        <v>76</v>
+        <v>80.2</v>
       </c>
       <c r="AG46" t="n">
         <v>91.7713640807246</v>
@@ -6867,7 +6867,7 @@
         <v>-0.3006103</v>
       </c>
       <c r="H47" t="n">
-        <v>3001.16311951334</v>
+        <v>3070.79580931865</v>
       </c>
       <c r="I47" t="n">
         <v>3.102381927103863</v>
@@ -6879,7 +6879,7 @@
         <v>44.9</v>
       </c>
       <c r="L47" t="n">
-        <v>29.34050751</v>
+        <v>24.30197856093</v>
       </c>
       <c r="M47" t="n">
         <v>96.48000335693359</v>
@@ -6937,7 +6937,7 @@
         <v>77.7584980237154</v>
       </c>
       <c r="AF47" t="n">
-        <v>57.3</v>
+        <v>60.6</v>
       </c>
       <c r="AG47" t="n">
         <v>78.0789963759688</v>
@@ -6971,7 +6971,7 @@
         <v>0.1649292</v>
       </c>
       <c r="H48" t="n">
-        <v>11686.6020661881</v>
+        <v>11697.9201596588</v>
       </c>
       <c r="I48" t="n">
         <v>4.50074083390312</v>
@@ -6983,7 +6983,7 @@
         <v>59.1</v>
       </c>
       <c r="L48" t="n">
-        <v>20.20207024</v>
+        <v>54.7085229571242</v>
       </c>
       <c r="M48" t="n">
         <v>92.129997253418</v>
@@ -7041,7 +7041,7 @@
         <v>47.142562159142</v>
       </c>
       <c r="AF48" t="n">
-        <v>56.7</v>
+        <v>59.3</v>
       </c>
       <c r="AG48" t="n">
         <v>86.5087378352127</v>
@@ -7075,7 +7075,7 @@
         <v>-0.6292553</v>
       </c>
       <c r="H49" t="n">
-        <v>11799.2028793201</v>
+        <v>11822.961305357</v>
       </c>
       <c r="I49" t="n">
         <v>2.316757362894658</v>
@@ -7087,7 +7087,7 @@
         <v>54.6</v>
       </c>
       <c r="L49" t="n">
-        <v>6.704431057</v>
+        <v>21.6231408755943</v>
       </c>
       <c r="M49" t="n">
         <v>98.6600036621094</v>
@@ -7145,7 +7145,7 @@
         <v>69.4767441860465</v>
       </c>
       <c r="AF49" t="n">
-        <v>86.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="AG49" t="n">
         <v>80.3737107191052</v>
@@ -7179,7 +7179,7 @@
         <v>-0.2095917</v>
       </c>
       <c r="H50" t="n">
-        <v>15456.1989933658</v>
+        <v>15478.6456794969</v>
       </c>
       <c r="I50" t="n">
         <v>1.133028233261703</v>
@@ -7191,7 +7191,7 @@
         <v>54.1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3649131358</v>
+        <v>54.7085229571242</v>
       </c>
       <c r="M50" t="n">
         <v>97.1699981689453</v>
@@ -7251,7 +7251,7 @@
         <v>79.4178502831612</v>
       </c>
       <c r="AF50" t="n">
-        <v>87.7</v>
+        <v>90.2</v>
       </c>
       <c r="AG50" t="n">
         <v>90.19168013647391</v>
@@ -7285,7 +7285,7 @@
         <v>-1.15283659999999</v>
       </c>
       <c r="H51" t="n">
-        <v>3958.53228789687</v>
+        <v>4047.95264193561</v>
       </c>
       <c r="I51" t="n">
         <v>2.980379970186107</v>
@@ -7297,7 +7297,7 @@
         <v>30.3</v>
       </c>
       <c r="L51" t="n">
-        <v>7.503285010666666</v>
+        <v>15.3194009591458</v>
       </c>
       <c r="M51" t="n">
         <v>90.83695658878889</v>
@@ -7353,7 +7353,7 @@
         <v>71.46695325094041</v>
       </c>
       <c r="AF51" t="n">
-        <v>89.8</v>
+        <v>91.7</v>
       </c>
       <c r="AG51" t="n">
         <v>85.05392785893019</v>
@@ -7387,7 +7387,7 @@
         <v>-0.9853603</v>
       </c>
       <c r="H52" t="n">
-        <v>1883.5374311384</v>
+        <v>1888.66403175151</v>
       </c>
       <c r="I52" t="n">
         <v>4.23041281246881</v>
@@ -7399,7 +7399,7 @@
         <v>36.8</v>
       </c>
       <c r="L52" t="n">
-        <v>9.398294449</v>
+        <v>16.4779381826938</v>
       </c>
       <c r="M52" t="n">
         <v>82.379997253418</v>
@@ -7457,7 +7457,7 @@
         <v>70.2904778274321</v>
       </c>
       <c r="AF52" t="n">
-        <v>39.4</v>
+        <v>42.5</v>
       </c>
       <c r="AG52" t="n">
         <v>55.3389608321256</v>
@@ -7491,7 +7491,7 @@
         <v>0.3417899</v>
       </c>
       <c r="H53" t="n">
-        <v>25178.56695837833</v>
+        <v>25053.79184106153</v>
       </c>
       <c r="I53" t="n">
         <v>5.996689350628293</v>
@@ -7503,7 +7503,7 @@
         <v>36.8</v>
       </c>
       <c r="L53" t="n">
-        <v>9.436307907</v>
+        <v>54.7085229571242</v>
       </c>
       <c r="M53" t="n">
         <v>99.80101459669299</v>
@@ -7593,7 +7593,7 @@
         <v>1.151735</v>
       </c>
       <c r="H54" t="n">
-        <v>25178.56695837833</v>
+        <v>25053.79184106153</v>
       </c>
       <c r="I54" t="n">
         <v>6.135655973449707</v>
@@ -7605,7 +7605,7 @@
         <v>32.1</v>
       </c>
       <c r="L54" t="n">
-        <v>3.675252676</v>
+        <v>24.5166106524244</v>
       </c>
       <c r="M54" t="n">
         <v>98.9700012207031</v>
@@ -7695,7 +7695,7 @@
         <v>0.1218554</v>
       </c>
       <c r="H55" t="n">
-        <v>6241.85614464638</v>
+        <v>6274.34741942922</v>
       </c>
       <c r="I55" t="n">
         <v>0.6732799255816667</v>
@@ -7707,7 +7707,7 @@
         <v>40.7</v>
       </c>
       <c r="L55" t="n">
-        <v>7.503285010666666</v>
+        <v>7.81631512865351</v>
       </c>
       <c r="M55" t="n">
         <v>95.4899978637695</v>
@@ -7761,7 +7761,7 @@
         <v>44.7916666666667</v>
       </c>
       <c r="AF55" t="n">
-        <v>81.3</v>
+        <v>77.7</v>
       </c>
       <c r="AG55" t="n">
         <v>77.957445837032</v>
@@ -7781,7 +7781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7860,12 +7860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7874,21 +7874,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E4" t="n">
-        <v>9.242378</v>
+        <v>93.769997</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7897,21 +7897,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>61.363697</v>
+        <v>65.80999799999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="E6" t="n">
-        <v>2.077909</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7946,7 +7946,7 @@
         <v>2008</v>
       </c>
       <c r="E7" t="n">
-        <v>93.769997</v>
+        <v>86.970001</v>
       </c>
     </row>
     <row r="8">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7969,18 +7969,18 @@
         <v>2008</v>
       </c>
       <c r="E8" t="n">
-        <v>65.80999799999999</v>
+        <v>36.700001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7989,21 +7989,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="E9" t="n">
-        <v>78.56999999999999</v>
+        <v>97.80391</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8012,21 +8012,21 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E10" t="n">
-        <v>86.970001</v>
+        <v>71.25324000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E11" t="n">
-        <v>36.700001</v>
+        <v>64.13782999999999</v>
       </c>
     </row>
     <row r="12">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>97.80391</v>
+        <v>78.02392999999999</v>
       </c>
     </row>
     <row r="13">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E13" t="n">
-        <v>71.25324000000001</v>
+        <v>66.29549</v>
       </c>
     </row>
     <row r="14">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8104,10 +8104,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>64.13782999999999</v>
+        <v>87.88284</v>
       </c>
     </row>
     <row r="15">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>78.02392999999999</v>
+        <v>79.96782</v>
       </c>
     </row>
     <row r="16">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E16" t="n">
-        <v>66.29549</v>
+        <v>95.49324</v>
       </c>
     </row>
     <row r="17">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E17" t="n">
-        <v>87.88284</v>
+        <v>94.14912</v>
       </c>
     </row>
     <row r="18">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8196,21 +8196,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="E18" t="n">
-        <v>79.96782</v>
+        <v>87.65678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8219,21 +8219,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E19" t="n">
-        <v>95.49324</v>
+        <v>31.4995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E20" t="n">
-        <v>94.14912</v>
+        <v>32.20633</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="E21" t="n">
-        <v>87.65678</v>
+        <v>11.29064</v>
       </c>
     </row>
     <row r="22">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8288,21 +8288,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="E22" t="n">
-        <v>31.4995</v>
+        <v>48.73362</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8311,21 +8311,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>32.20633</v>
+        <v>65.53286</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8334,21 +8334,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E24" t="n">
-        <v>11.29064</v>
+        <v>90.438362</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E25" t="n">
-        <v>48.73362</v>
+        <v>81.92336299999999</v>
       </c>
     </row>
     <row r="26">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8383,18 +8383,18 @@
         <v>2011</v>
       </c>
       <c r="E26" t="n">
-        <v>65.53286</v>
+        <v>50.83765</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>primary_gpi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8403,21 +8403,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>90.438362</v>
+        <v>0.93111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8426,21 +8426,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E28" t="n">
-        <v>81.92336299999999</v>
+        <v>1.03872</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8449,21 +8449,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="E29" t="n">
-        <v>50.83765</v>
+        <v>0.95989</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>primary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8472,21 +8472,21 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="E30" t="n">
-        <v>0.93111</v>
+        <v>5.061457</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8495,21 +8495,21 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>1.03872</v>
+        <v>3.087095</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E32" t="n">
-        <v>0.95989</v>
+        <v>4.41784</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="E33" t="n">
-        <v>5.061457</v>
+        <v>15.607567</v>
       </c>
     </row>
     <row r="34">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8567,7 +8567,7 @@
         <v>2012</v>
       </c>
       <c r="E34" t="n">
-        <v>3.087095</v>
+        <v>8.510548</v>
       </c>
     </row>
     <row r="35">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8590,7 +8590,7 @@
         <v>2012</v>
       </c>
       <c r="E35" t="n">
-        <v>4.41784</v>
+        <v>1.775987</v>
       </c>
     </row>
     <row r="36">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>15.607567</v>
+        <v>3.589998</v>
       </c>
     </row>
     <row r="37">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8636,7 +8636,7 @@
         <v>2012</v>
       </c>
       <c r="E37" t="n">
-        <v>8.510548</v>
+        <v>13.982581</v>
       </c>
     </row>
     <row r="38">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8656,21 +8656,21 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E38" t="n">
-        <v>1.775987</v>
+        <v>3.231897</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="E39" t="n">
-        <v>3.589998</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8702,21 +8702,21 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="E40" t="n">
-        <v>13.982581</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8725,21 +8725,21 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E41" t="n">
-        <v>3.231897</v>
+        <v>41.013363</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E42" t="n">
-        <v>23000</v>
+        <v>7.448156</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="E43" t="n">
-        <v>10000</v>
+        <v>29.679646</v>
       </c>
     </row>
     <row r="44">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="E44" t="n">
-        <v>41.013363</v>
+        <v>8.914797</v>
       </c>
     </row>
     <row r="45">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8820,87 +8820,81 @@
         <v>2009</v>
       </c>
       <c r="E45" t="n">
-        <v>7.448156</v>
+        <v>6.241508</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>social_protection_labour_pop</t>
+          <t>inflation_5yr_avg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>stage1_extended</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2007</v>
-      </c>
+          <t>stage2_regional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>29.679646</v>
+        <v>28.415221</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>social_protection_labour_pop</t>
+          <t>inflation_5yr_avg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>stage1_extended</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>2005</v>
-      </c>
+          <t>stage2_regional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>8.914797</v>
+        <v>28.415221</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>social_protection_labour_pop</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>stage1_extended</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2009</v>
-      </c>
+          <t>stage2_regional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>6.241508</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>inflation_5yr_avg</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8910,18 +8904,18 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>28.415221</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>inflation_5yr_avg</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8931,18 +8925,18 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>28.415221</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gini</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8952,18 +8946,18 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>42.1</v>
+        <v>72.68142899999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gini</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8973,18 +8967,18 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>42.1</v>
+        <v>88.410174</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gini</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8994,18 +8988,18 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>32.7</v>
+        <v>96.110001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9015,18 +9009,18 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>15.398272</v>
+        <v>73.618723</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9036,18 +9030,18 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>7.503285</v>
+        <v>73.618723</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9057,18 +9051,18 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>7.503285</v>
+        <v>79.44973400000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9078,13 +9072,13 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>7.437257</v>
+        <v>79.44973400000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9099,18 +9093,18 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>7.437257</v>
+        <v>90.315206</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9120,18 +9114,18 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>72.68142899999999</v>
+        <v>22.21478</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9141,18 +9135,18 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>88.410174</v>
+        <v>22.21478</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9162,18 +9156,18 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>96.110001</v>
+        <v>22.21478</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9183,18 +9177,18 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>73.618723</v>
+        <v>22.21478</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9204,18 +9198,18 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>73.618723</v>
+        <v>30.788238</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9225,18 +9219,18 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>79.44973400000001</v>
+        <v>30.788238</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9246,18 +9240,18 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>79.44973400000001</v>
+        <v>30.788238</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9267,7 +9261,7 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>90.315206</v>
+        <v>30.788238</v>
       </c>
     </row>
     <row r="67">
@@ -9278,7 +9272,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9288,7 +9282,7 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>22.21478</v>
+        <v>59.589417</v>
       </c>
     </row>
     <row r="68">
@@ -9299,7 +9293,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9309,7 +9303,7 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>22.21478</v>
+        <v>59.589417</v>
       </c>
     </row>
     <row r="69">
@@ -9320,7 +9314,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9330,7 +9324,7 @@
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>22.21478</v>
+        <v>59.589417</v>
       </c>
     </row>
     <row r="70">
@@ -9341,7 +9335,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9351,7 +9345,7 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>22.21478</v>
+        <v>51.659543</v>
       </c>
     </row>
     <row r="71">
@@ -9362,7 +9356,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9372,7 +9366,7 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>30.788238</v>
+        <v>51.659543</v>
       </c>
     </row>
     <row r="72">
@@ -9383,7 +9377,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9393,7 +9387,7 @@
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>30.788238</v>
+        <v>38.059195</v>
       </c>
     </row>
     <row r="73">
@@ -9404,7 +9398,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9414,7 +9408,7 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>30.788238</v>
+        <v>38.059195</v>
       </c>
     </row>
     <row r="74">
@@ -9425,7 +9419,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9435,18 +9429,18 @@
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>30.788238</v>
+        <v>38.059195</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9456,18 +9450,18 @@
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>59.589417</v>
+        <v>72.727248</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9477,18 +9471,18 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>59.589417</v>
+        <v>72.727248</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9498,18 +9492,18 @@
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>59.589417</v>
+        <v>72.727248</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9519,18 +9513,18 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>51.659543</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9540,18 +9534,18 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>51.659543</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9561,18 +9555,18 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>38.059195</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9582,18 +9576,18 @@
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>38.059195</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9603,7 +9597,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>38.059195</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="83">
@@ -9614,7 +9608,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9624,7 +9618,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>72.727248</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="84">
@@ -9635,7 +9629,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9645,7 +9639,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>72.727248</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="85">
@@ -9656,7 +9650,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9666,7 +9660,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>72.727248</v>
+        <v>89.184482</v>
       </c>
     </row>
     <row r="86">
@@ -9677,7 +9671,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9698,7 +9692,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9708,7 +9702,7 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>89.184482</v>
+        <v>60.470556</v>
       </c>
     </row>
     <row r="88">
@@ -9719,7 +9713,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9729,7 +9723,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>89.184482</v>
+        <v>60.470556</v>
       </c>
     </row>
     <row r="89">
@@ -9740,7 +9734,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9750,7 +9744,7 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>89.184482</v>
+        <v>60.470556</v>
       </c>
     </row>
     <row r="90">
@@ -9761,7 +9755,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9771,7 +9765,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>89.184482</v>
+        <v>76.584614</v>
       </c>
     </row>
     <row r="91">
@@ -9782,7 +9776,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9792,7 +9786,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>89.184482</v>
+        <v>76.584614</v>
       </c>
     </row>
     <row r="92">
@@ -9803,7 +9797,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9813,7 +9807,7 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>89.184482</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9824,7 +9818,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9834,7 +9828,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>89.184482</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="94">
@@ -9845,7 +9839,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9855,7 +9849,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>89.184482</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="95">
@@ -9866,7 +9860,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9876,7 +9870,7 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>60.470556</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="96">
@@ -9887,7 +9881,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9897,7 +9891,7 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>60.470556</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="97">
@@ -9908,7 +9902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9918,7 +9912,7 @@
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>60.470556</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="98">
@@ -9929,7 +9923,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9939,7 +9933,7 @@
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>76.584614</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="99">
@@ -9950,7 +9944,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9960,18 +9954,18 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>76.584614</v>
+        <v>77.91236000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>primary_gpi</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -9981,18 +9975,18 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>77.91236000000001</v>
+        <v>0.957248</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>primary_gpi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10002,18 +9996,18 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>77.91236000000001</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10023,18 +10017,18 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="n">
-        <v>77.91236000000001</v>
+        <v>0.8055369999999999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10044,18 +10038,18 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>77.91236000000001</v>
+        <v>0.953613</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10065,18 +10059,18 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>77.91236000000001</v>
+        <v>0.953613</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10086,18 +10080,18 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>77.91236000000001</v>
+        <v>0.953613</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10107,18 +10101,18 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>77.91236000000001</v>
+        <v>1.032342</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10128,18 +10122,18 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>77.91236000000001</v>
+        <v>1.108339</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>primary_gpi</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10149,18 +10143,18 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>0.957248</v>
+        <v>0.958604</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>primary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10170,18 +10164,18 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>0.9728</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10191,18 +10185,18 @@
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>0.8055369999999999</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10212,18 +10206,18 @@
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.953613</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10233,18 +10227,18 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.953613</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10254,18 +10248,18 @@
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>0.953613</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10275,18 +10269,18 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>1.032342</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -10296,18 +10290,18 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>1.108339</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10317,7 +10311,7 @@
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>0.958604</v>
+        <v>2.386668</v>
       </c>
     </row>
     <row r="117">
@@ -10328,7 +10322,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -10349,7 +10343,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10359,7 +10353,7 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>2.386668</v>
+        <v>0.849899</v>
       </c>
     </row>
     <row r="119">
@@ -10370,7 +10364,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10380,7 +10374,7 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>2.386668</v>
+        <v>0.849899</v>
       </c>
     </row>
     <row r="120">
@@ -10391,7 +10385,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10401,7 +10395,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>2.386668</v>
+        <v>8.901687000000001</v>
       </c>
     </row>
     <row r="121">
@@ -10412,7 +10406,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10422,7 +10416,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>2.386668</v>
+        <v>8.901687000000001</v>
       </c>
     </row>
     <row r="122">
@@ -10433,7 +10427,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10443,7 +10437,7 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>2.386668</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="123">
@@ -10454,7 +10448,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10464,7 +10458,7 @@
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>2.386668</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="124">
@@ -10475,7 +10469,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10485,7 +10479,7 @@
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>2.386668</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="125">
@@ -10496,7 +10490,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10506,7 +10500,7 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>2.386668</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="126">
@@ -10517,7 +10511,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10527,7 +10521,7 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>0.849899</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="127">
@@ -10538,7 +10532,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10548,7 +10542,7 @@
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>0.849899</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="128">
@@ -10559,7 +10553,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10569,7 +10563,7 @@
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
-        <v>8.901687000000001</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="129">
@@ -10580,7 +10574,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10590,7 +10584,7 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>8.901687000000001</v>
+        <v>3.685359</v>
       </c>
     </row>
     <row r="130">
@@ -10601,7 +10595,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10622,7 +10616,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10643,7 +10637,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10664,7 +10658,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10685,7 +10679,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10701,12 +10695,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10716,18 +10710,18 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
-        <v>3.685359</v>
+        <v>17.576451</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10737,18 +10731,18 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>3.685359</v>
+        <v>17.576451</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10758,18 +10752,18 @@
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>3.685359</v>
+        <v>17.576451</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -10779,18 +10773,18 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
-        <v>3.685359</v>
+        <v>17.576451</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10800,18 +10794,18 @@
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
-        <v>3.685359</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10821,18 +10815,18 @@
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>3.685359</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10842,18 +10836,18 @@
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>3.685359</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10863,7 +10857,7 @@
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>3.685359</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="143">
@@ -10874,7 +10868,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10884,7 +10878,7 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>17.576451</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="144">
@@ -10895,7 +10889,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10905,7 +10899,7 @@
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
-        <v>17.576451</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="145">
@@ -10916,7 +10910,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10926,7 +10920,7 @@
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>17.576451</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="146">
@@ -10937,7 +10931,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10947,7 +10941,7 @@
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>17.576451</v>
+        <v>22.359148</v>
       </c>
     </row>
     <row r="147">
@@ -10958,7 +10952,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10968,7 +10962,7 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>22.359148</v>
+        <v>41.146088</v>
       </c>
     </row>
     <row r="148">
@@ -10979,7 +10973,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10989,7 +10983,7 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>22.359148</v>
+        <v>41.146088</v>
       </c>
     </row>
     <row r="149">
@@ -11000,7 +10994,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11010,7 +11004,7 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="n">
-        <v>22.359148</v>
+        <v>73.232314</v>
       </c>
     </row>
     <row r="150">
@@ -11021,7 +11015,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11031,7 +11025,7 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
-        <v>22.359148</v>
+        <v>73.232314</v>
       </c>
     </row>
     <row r="151">
@@ -11042,7 +11036,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11052,7 +11046,7 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>22.359148</v>
+        <v>50.208846</v>
       </c>
     </row>
     <row r="152">
@@ -11063,7 +11057,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11073,7 +11067,7 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>22.359148</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="153">
@@ -11084,7 +11078,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11094,7 +11088,7 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>22.359148</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="154">
@@ -11105,7 +11099,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11115,7 +11109,7 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>22.359148</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="155">
@@ -11126,7 +11120,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11136,7 +11130,7 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>41.146088</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="156">
@@ -11147,7 +11141,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11157,7 +11151,7 @@
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>41.146088</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="157">
@@ -11168,7 +11162,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11178,7 +11172,7 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>73.232314</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="158">
@@ -11189,7 +11183,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11199,18 +11193,18 @@
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>73.232314</v>
+        <v>28.640838</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11220,18 +11214,18 @@
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="n">
-        <v>50.208846</v>
+        <v>23.959397</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11241,18 +11235,18 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>28.640838</v>
+        <v>38.871546</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11262,18 +11256,18 @@
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>28.640838</v>
+        <v>38.871546</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11283,18 +11277,18 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>28.640838</v>
+        <v>75.265237</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11304,18 +11298,18 @@
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>28.640838</v>
+        <v>37.285302</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11325,18 +11319,18 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>28.640838</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11346,18 +11340,18 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>28.640838</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11367,13 +11361,13 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>28.640838</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11388,18 +11382,18 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
-        <v>23.959397</v>
+        <v>29.836364</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11409,18 +11403,18 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>38.871546</v>
+        <v>29.836364</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11430,13 +11424,13 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>38.871546</v>
+        <v>29.836364</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11451,18 +11445,18 @@
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>75.265237</v>
+        <v>10.925</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11472,7 +11466,7 @@
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>37.285302</v>
+        <v>10.925</v>
       </c>
     </row>
     <row r="172">
@@ -11483,7 +11477,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11493,18 +11487,18 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>35.98</v>
+        <v>13.946667</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11514,18 +11508,18 @@
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>35.98</v>
+        <v>10.326252</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11535,18 +11529,18 @@
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>35.98</v>
+        <v>10.326252</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11556,18 +11550,18 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>29.836364</v>
+        <v>10.326252</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11577,18 +11571,18 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>29.836364</v>
+        <v>10.326252</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11598,18 +11592,18 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>29.836364</v>
+        <v>10.326252</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11619,18 +11613,18 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>10.925</v>
+        <v>6.856892</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11640,18 +11634,18 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="n">
-        <v>10.925</v>
+        <v>6.856892</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11661,7 +11655,7 @@
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>13.946667</v>
+        <v>4.490364</v>
       </c>
     </row>
     <row r="181">
@@ -11672,7 +11666,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11682,7 +11676,7 @@
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>10.326252</v>
+        <v>4.490364</v>
       </c>
     </row>
     <row r="182">
@@ -11693,7 +11687,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11703,7 +11697,7 @@
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>10.326252</v>
+        <v>2.217771</v>
       </c>
     </row>
     <row r="183">
@@ -11714,7 +11708,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11724,7 +11718,7 @@
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>10.326252</v>
+        <v>2.217771</v>
       </c>
     </row>
     <row r="184">
@@ -11735,7 +11729,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11745,7 +11739,7 @@
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>10.326252</v>
+        <v>19.702696</v>
       </c>
     </row>
     <row r="185">
@@ -11756,7 +11750,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11766,7 +11760,7 @@
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="n">
-        <v>10.326252</v>
+        <v>3.551444</v>
       </c>
     </row>
     <row r="186">
@@ -11777,7 +11771,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11787,7 +11781,7 @@
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>6.856892</v>
+        <v>3.551444</v>
       </c>
     </row>
     <row r="187">
@@ -11798,7 +11792,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11808,7 +11802,7 @@
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>6.856892</v>
+        <v>3.551444</v>
       </c>
     </row>
     <row r="188">
@@ -11819,7 +11813,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11829,7 +11823,7 @@
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="n">
-        <v>4.490364</v>
+        <v>3.551444</v>
       </c>
     </row>
     <row r="189">
@@ -11840,7 +11834,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11850,18 +11844,18 @@
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="n">
-        <v>4.490364</v>
+        <v>3.551444</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11871,18 +11865,18 @@
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>2.217771</v>
+        <v>40.663704</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11892,18 +11886,18 @@
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="n">
-        <v>2.217771</v>
+        <v>40.663704</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11913,18 +11907,18 @@
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>19.702696</v>
+        <v>40.663704</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11934,18 +11928,18 @@
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="n">
-        <v>3.551444</v>
+        <v>25.822737</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11955,18 +11949,18 @@
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="n">
-        <v>3.551444</v>
+        <v>25.822737</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11976,18 +11970,18 @@
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
-        <v>3.551444</v>
+        <v>25.822737</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11997,18 +11991,18 @@
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="n">
-        <v>3.551444</v>
+        <v>60.929992</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12018,7 +12012,7 @@
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>3.551444</v>
+        <v>60.929992</v>
       </c>
     </row>
     <row r="198">
@@ -12029,7 +12023,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12039,7 +12033,7 @@
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>40.663704</v>
+        <v>12.497846</v>
       </c>
     </row>
     <row r="199">
@@ -12050,7 +12044,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12060,7 +12054,7 @@
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="n">
-        <v>40.663704</v>
+        <v>12.497846</v>
       </c>
     </row>
     <row r="200">
@@ -12071,7 +12065,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12081,7 +12075,7 @@
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="n">
-        <v>40.663704</v>
+        <v>12.497846</v>
       </c>
     </row>
     <row r="201">
@@ -12092,7 +12086,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12102,18 +12096,18 @@
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>25.822737</v>
+        <v>12.497846</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>co2_pc</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12123,18 +12117,18 @@
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="n">
-        <v>25.822737</v>
+        <v>0.31881</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>freshwater_withdraw</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12144,18 +12138,18 @@
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="n">
-        <v>25.822737</v>
+        <v>7.419067</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12165,18 +12159,18 @@
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="n">
-        <v>60.929992</v>
+        <v>17.269631</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12186,18 +12180,18 @@
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
-        <v>60.929992</v>
+        <v>17.269631</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12207,18 +12201,18 @@
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="n">
-        <v>12.497846</v>
+        <v>16.94175</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12228,18 +12222,18 @@
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="n">
-        <v>12.497846</v>
+        <v>20.25105</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12249,18 +12243,18 @@
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
-        <v>12.497846</v>
+        <v>37.01863</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12270,174 +12264,6 @@
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="n">
-        <v>12.497846</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>co2_pc</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>SSD</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="n">
-        <v>0.31881</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>freshwater_withdraw</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>SYC</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="n">
-        <v>7.419067</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="n">
-        <v>17.269631</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>GNQ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="n">
-        <v>17.269631</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>ERI</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="n">
-        <v>16.94175</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>SYC</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="n">
-        <v>20.25105</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>DZA</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="n">
-        <v>37.01863</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>social_protection_labour_pop</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>LBY</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>stage2_regional</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="n">
         <v>37.01863</v>
       </c>
     </row>
@@ -12506,7 +12332,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0008</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="4">
@@ -12586,7 +12412,7 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6501</v>
       </c>
     </row>
   </sheetData>
@@ -12648,191 +12474,191 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>hand_washing_facil</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.8</v>
+        <v>18.5255</v>
       </c>
       <c r="C2" t="n">
-        <v>76.15000000000001</v>
+        <v>43.9048</v>
       </c>
       <c r="D2" t="n">
-        <v>27.35</v>
+        <v>25.3793</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.9</v>
+        <v>-32.233</v>
       </c>
       <c r="F2" t="n">
-        <v>130.85</v>
+        <v>94.66330000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inflation_5yr_avg</t>
+          <t>sev_food_insec</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.002</v>
+        <v>10.925</v>
       </c>
       <c r="C3" t="n">
-        <v>14.7713</v>
+        <v>29.8364</v>
       </c>
       <c r="D3" t="n">
-        <v>10.7692</v>
+        <v>18.9114</v>
       </c>
       <c r="E3" t="n">
-        <v>-17.5364</v>
+        <v>-26.8977</v>
       </c>
       <c r="F3" t="n">
-        <v>36.3097</v>
+        <v>67.6591</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rq_estimate</t>
+          <t>primary_gpi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.9893999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4118</v>
+        <v>1.0124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5776</v>
+        <v>0.0795</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1446</v>
+        <v>0.774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7433999999999999</v>
+        <v>1.1713</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>co2_pc</t>
+          <t>learning_poverty</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1868</v>
+        <v>72.7272</v>
       </c>
       <c r="C5" t="n">
-        <v>1.155</v>
+        <v>89.1845</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9681999999999999</v>
+        <v>16.4572</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7497</v>
+        <v>39.8128</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0914</v>
+        <v>122.0989</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>primary_gpi</t>
+          <t>freshwater_withdraw</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9329</v>
+        <v>1.3138</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0124</v>
+        <v>22.4265</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0795</v>
+        <v>21.1128</v>
       </c>
       <c r="E6" t="n">
-        <v>0.774</v>
+        <v>-40.9118</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1713</v>
+        <v>64.6521</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hand_washing_facil</t>
+          <t>secondary_gpi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.5255</v>
+        <v>0.9053</v>
       </c>
       <c r="C7" t="n">
-        <v>43.9048</v>
+        <v>1.0853</v>
       </c>
       <c r="D7" t="n">
-        <v>25.3793</v>
+        <v>0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>-32.233</v>
+        <v>0.5453</v>
       </c>
       <c r="F7" t="n">
-        <v>94.66330000000001</v>
+        <v>1.4453</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gini</t>
+          <t>water_access_pop</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.625</v>
+        <v>64.69589999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>42.925</v>
+        <v>86.95480000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>8.300000000000001</v>
+        <v>22.2589</v>
       </c>
       <c r="E8" t="n">
-        <v>18.025</v>
+        <v>20.1782</v>
       </c>
       <c r="F8" t="n">
-        <v>59.525</v>
+        <v>131.4725</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -12844,26 +12670,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>primary_enroll</t>
+          <t>life_expect_tot</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.0596</v>
+        <v>62.1635</v>
       </c>
       <c r="C9" t="n">
-        <v>93.39409999999999</v>
+        <v>68.505</v>
       </c>
       <c r="D9" t="n">
-        <v>19.3345</v>
+        <v>6.3415</v>
       </c>
       <c r="E9" t="n">
-        <v>35.3905</v>
+        <v>49.4805</v>
       </c>
       <c r="F9" t="n">
-        <v>132.0631</v>
+        <v>81.188</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12872,23 +12698,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>va_estimate</t>
+          <t>mort_infant</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.2381</v>
+        <v>27.8</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2874</v>
+        <v>46.925</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9507</v>
+        <v>19.125</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1396</v>
+        <v>-10.45</v>
       </c>
       <c r="F10" t="n">
-        <v>1.614</v>
+        <v>85.175</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -12900,54 +12726,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>freshwater_withdraw</t>
+          <t>agri_land</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3138</v>
+        <v>32.5705</v>
       </c>
       <c r="C11" t="n">
-        <v>22.4265</v>
+        <v>68.7938</v>
       </c>
       <c r="D11" t="n">
-        <v>21.1128</v>
+        <v>36.2233</v>
       </c>
       <c r="E11" t="n">
-        <v>-40.9118</v>
+        <v>-39.8762</v>
       </c>
       <c r="F11" t="n">
-        <v>64.6521</v>
+        <v>141.2405</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>water_access_pop</t>
+          <t>gdp_growth_3yr_avg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64.69589999999999</v>
+        <v>3.0071</v>
       </c>
       <c r="C12" t="n">
-        <v>86.95480000000001</v>
+        <v>5.4095</v>
       </c>
       <c r="D12" t="n">
-        <v>22.2589</v>
+        <v>2.4024</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1782</v>
+        <v>-1.7976</v>
       </c>
       <c r="F12" t="n">
-        <v>131.4725</v>
+        <v>10.2142</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12956,23 +12782,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pv_estimate</t>
+          <t>va_estimate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.3848</v>
+        <v>-1.2381</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2088</v>
+        <v>-0.2874</v>
       </c>
       <c r="D13" t="n">
-        <v>1.176</v>
+        <v>0.9507</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7369</v>
+        <v>-3.1396</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1433</v>
+        <v>1.614</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -12984,51 +12810,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>managed_water_percent</t>
+          <t>nonrenew_elec</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.1318</v>
+        <v>27.4792</v>
       </c>
       <c r="C14" t="n">
-        <v>41.1461</v>
+        <v>91.8817</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0143</v>
+        <v>64.40260000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8968</v>
+        <v>-101.3259</v>
       </c>
       <c r="F14" t="n">
-        <v>79.1747</v>
+        <v>220.6868</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>youth_literacy</t>
+          <t>social_protection_labour_pop</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71.2967</v>
+        <v>10.3687</v>
       </c>
       <c r="C15" t="n">
-        <v>92.41500000000001</v>
+        <v>36.9497</v>
       </c>
       <c r="D15" t="n">
-        <v>21.1183</v>
+        <v>26.581</v>
       </c>
       <c r="E15" t="n">
-        <v>29.06</v>
+        <v>-42.7934</v>
       </c>
       <c r="F15" t="n">
-        <v>134.6517</v>
+        <v>90.1117</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -13040,79 +12866,79 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sev_food_insec</t>
+          <t>inflation_5yr_avg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.925</v>
+        <v>4.002</v>
       </c>
       <c r="C16" t="n">
-        <v>29.8364</v>
+        <v>14.7713</v>
       </c>
       <c r="D16" t="n">
-        <v>18.9114</v>
+        <v>10.7692</v>
       </c>
       <c r="E16" t="n">
-        <v>-26.8977</v>
+        <v>-17.5364</v>
       </c>
       <c r="F16" t="n">
-        <v>67.6591</v>
+        <v>36.3097</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rl_estimate</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.1916</v>
+        <v>2.3735</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3915</v>
+        <v>3.6854</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1.3118</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7916</v>
+        <v>-0.2502</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2085</v>
+        <v>6.3091</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>intent_homicide</t>
+          <t>managed_water_percent</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4761</v>
+        <v>22.1318</v>
       </c>
       <c r="C18" t="n">
-        <v>9.988</v>
+        <v>41.1461</v>
       </c>
       <c r="D18" t="n">
-        <v>7.5118</v>
+        <v>19.0143</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.5475</v>
+        <v>-15.8968</v>
       </c>
       <c r="F18" t="n">
-        <v>25.0116</v>
+        <v>79.1747</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -13124,135 +12950,135 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>intent_homicide</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.4251</v>
+        <v>2.4761</v>
       </c>
       <c r="C19" t="n">
-        <v>20.5202</v>
+        <v>9.988</v>
       </c>
       <c r="D19" t="n">
-        <v>13.0951</v>
+        <v>7.5118</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.765</v>
+        <v>-12.5475</v>
       </c>
       <c r="F19" t="n">
-        <v>46.7104</v>
+        <v>25.0116</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>cc_estimate</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3735</v>
+        <v>-1.1462</v>
       </c>
       <c r="C20" t="n">
-        <v>3.6854</v>
+        <v>-0.2973</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3118</v>
+        <v>0.849</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2502</v>
+        <v>-2.8441</v>
       </c>
       <c r="F20" t="n">
-        <v>6.3091</v>
+        <v>1.4006</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>secondary_gpi</t>
+          <t>gdp_pc_ppp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9053</v>
+        <v>2943.4806</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0853</v>
+        <v>10313.5843</v>
       </c>
       <c r="D21" t="n">
-        <v>0.18</v>
+        <v>7370.1038</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5453</v>
+        <v>-11796.727</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4453</v>
+        <v>25053.7918</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>displaced_persons</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.405</v>
+        <v>10.3753</v>
       </c>
       <c r="C22" t="n">
-        <v>30.5774</v>
+        <v>25.1531</v>
       </c>
       <c r="D22" t="n">
-        <v>30.1723</v>
+        <v>14.7777</v>
       </c>
       <c r="E22" t="n">
-        <v>-59.9396</v>
+        <v>-19.1801</v>
       </c>
       <c r="F22" t="n">
-        <v>90.922</v>
+        <v>54.7085</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mort_infant</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.8</v>
+        <v>34.625</v>
       </c>
       <c r="C23" t="n">
-        <v>46.925</v>
+        <v>42.925</v>
       </c>
       <c r="D23" t="n">
-        <v>19.125</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.45</v>
+        <v>18.025</v>
       </c>
       <c r="F23" t="n">
-        <v>85.175</v>
+        <v>59.525</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -13264,79 +13090,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gdp_pc_ppp</t>
+          <t>pv_estimate</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2922.2094</v>
+        <v>-1.3848</v>
       </c>
       <c r="C24" t="n">
-        <v>10340.9953</v>
+        <v>-0.2088</v>
       </c>
       <c r="D24" t="n">
-        <v>7418.7858</v>
+        <v>1.176</v>
       </c>
       <c r="E24" t="n">
-        <v>-11915.3623</v>
+        <v>-3.7369</v>
       </c>
       <c r="F24" t="n">
-        <v>25178.567</v>
+        <v>2.1433</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>secondary_enroll</t>
+          <t>co2_pc</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.8673</v>
+        <v>0.1868</v>
       </c>
       <c r="C25" t="n">
-        <v>49.9515</v>
+        <v>1.155</v>
       </c>
       <c r="D25" t="n">
-        <v>20.0842</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.3011</v>
+        <v>-1.7497</v>
       </c>
       <c r="F25" t="n">
-        <v>90.1199</v>
+        <v>3.0914</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>life_expect_tot</t>
+          <t>ge_estimate</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62.1635</v>
+        <v>-1.1413</v>
       </c>
       <c r="C26" t="n">
-        <v>68.505</v>
+        <v>-0.3145</v>
       </c>
       <c r="D26" t="n">
-        <v>6.3415</v>
+        <v>0.8269</v>
       </c>
       <c r="E26" t="n">
-        <v>49.4805</v>
+        <v>-2.7951</v>
       </c>
       <c r="F26" t="n">
-        <v>81.188</v>
+        <v>1.3393</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -13348,26 +13174,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>learning_poverty</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>72.7272</v>
+        <v>50.175</v>
       </c>
       <c r="C27" t="n">
-        <v>89.1845</v>
+        <v>79.575</v>
       </c>
       <c r="D27" t="n">
-        <v>16.4572</v>
+        <v>29.4</v>
       </c>
       <c r="E27" t="n">
-        <v>39.8128</v>
+        <v>-8.625</v>
       </c>
       <c r="F27" t="n">
-        <v>122.0989</v>
+        <v>138.375</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -13376,26 +13202,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gdp_growth_3yr_avg</t>
+          <t>rl_estimate</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.0071</v>
+        <v>-1.1916</v>
       </c>
       <c r="C28" t="n">
-        <v>5.4095</v>
+        <v>-0.3915</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4024</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.7976</v>
+        <v>-2.7916</v>
       </c>
       <c r="F28" t="n">
-        <v>10.2142</v>
+        <v>1.2085</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -13404,23 +13230,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cc_estimate</t>
+          <t>youth_literacy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1462</v>
+        <v>71.2967</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2973</v>
+        <v>92.41500000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.849</v>
+        <v>21.1183</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.8441</v>
+        <v>29.06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4006</v>
+        <v>134.6517</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -13432,26 +13258,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nonrenew_elec</t>
+          <t>primary_enroll</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.4792</v>
+        <v>74.0596</v>
       </c>
       <c r="C30" t="n">
-        <v>91.8817</v>
+        <v>93.39409999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>64.40260000000001</v>
+        <v>19.3345</v>
       </c>
       <c r="E30" t="n">
-        <v>-101.3259</v>
+        <v>35.3905</v>
       </c>
       <c r="F30" t="n">
-        <v>220.6868</v>
+        <v>132.0631</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -13460,23 +13286,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>social_protection_labour_pop</t>
+          <t>secondary_enroll</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10.3687</v>
+        <v>29.8673</v>
       </c>
       <c r="C31" t="n">
-        <v>36.9497</v>
+        <v>49.9515</v>
       </c>
       <c r="D31" t="n">
-        <v>26.581</v>
+        <v>20.0842</v>
       </c>
       <c r="E31" t="n">
-        <v>-42.7934</v>
+        <v>-10.3011</v>
       </c>
       <c r="F31" t="n">
-        <v>90.1117</v>
+        <v>90.1199</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -13488,57 +13314,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>agri_land</t>
+          <t>displaced_persons</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.5705</v>
+        <v>0.405</v>
       </c>
       <c r="C32" t="n">
-        <v>68.7938</v>
+        <v>30.5774</v>
       </c>
       <c r="D32" t="n">
-        <v>36.2233</v>
+        <v>30.1723</v>
       </c>
       <c r="E32" t="n">
-        <v>-39.8762</v>
+        <v>-59.9396</v>
       </c>
       <c r="F32" t="n">
-        <v>141.2405</v>
+        <v>90.922</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ge_estimate</t>
+          <t>rq_estimate</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1413</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3145</v>
+        <v>-0.4118</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8269</v>
+        <v>0.5776</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.7951</v>
+        <v>-2.1446</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3393</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13774,7 +13600,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
     </row>
@@ -13788,16 +13614,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.059</v>
+        <v>-0.058</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.307</v>
+        <v>-0.312</v>
       </c>
       <c r="E2" t="n">
         <v>-0.059</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.058</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="3">
@@ -13807,7 +13633,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.059</v>
+        <v>-0.058</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -13819,7 +13645,7 @@
         <v>-0.214</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.157</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="4">
@@ -13829,7 +13655,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.307</v>
+        <v>-0.312</v>
       </c>
       <c r="C4" t="n">
         <v>-0.174</v>
@@ -13841,7 +13667,7 @@
         <v>-0.004</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.166</v>
+        <v>-0.321</v>
       </c>
     </row>
     <row r="5">
@@ -13863,26 +13689,26 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.352</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.058</v>
+        <v>0.352</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.157</v>
+        <v>0.231</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.166</v>
+        <v>-0.321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.352</v>
+        <v>0.011</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
